--- a/data/trans_dic/P1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 15,79</t>
+          <t>7,94; 16,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 11,22</t>
+          <t>5,35; 11,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,21; 15,72</t>
+          <t>8,2; 16,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,18; 23,67</t>
+          <t>13,17; 23,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 17,91</t>
+          <t>8,95; 17,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 13,49</t>
+          <t>6,09; 13,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,7; 16,61</t>
+          <t>8,68; 17,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,57; 18,42</t>
+          <t>12,5; 18,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 15,02</t>
+          <t>9,26; 15,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,87</t>
+          <t>6,35; 11,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 15,06</t>
+          <t>9,32; 15,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,84; 20,53</t>
+          <t>13,58; 19,66</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,02</t>
+          <t>5,18; 10,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,27</t>
+          <t>3,35; 8,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 11,04</t>
+          <t>5,89; 10,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 19,5</t>
+          <t>11,9; 19,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 12,19</t>
+          <t>6,82; 12,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,56</t>
+          <t>5,07; 9,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,22</t>
+          <t>5,38; 10,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,29; 19,89</t>
+          <t>14,16; 20,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,31</t>
+          <t>6,65; 10,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,16</t>
+          <t>4,6; 7,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,62</t>
+          <t>6,15; 9,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,82; 18,58</t>
+          <t>13,92; 18,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 10,45</t>
+          <t>4,33; 10,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,95</t>
+          <t>5,19; 11,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,87</t>
+          <t>6,34; 12,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,03; 23,54</t>
+          <t>15,17; 23,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,17</t>
+          <t>5,99; 12,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 17,94</t>
+          <t>10,19; 17,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 18,06</t>
+          <t>10,44; 18,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,32; 25,21</t>
+          <t>18,08; 25,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 10,34</t>
+          <t>5,75; 10,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 13,42</t>
+          <t>8,53; 13,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 14,49</t>
+          <t>9,31; 14,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,46; 22,93</t>
+          <t>17,72; 23,01</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,7</t>
+          <t>3,37; 8,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,89</t>
+          <t>6,8; 13,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 15,2</t>
+          <t>8,33; 14,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,72; 28,23</t>
+          <t>16,85; 27,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 13,04</t>
+          <t>7,04; 13,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 12,44</t>
+          <t>6,24; 11,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 17,68</t>
+          <t>9,81; 17,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 22,32</t>
+          <t>10,02; 22,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,75</t>
+          <t>5,98; 10,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 11,67</t>
+          <t>7,24; 11,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 15,05</t>
+          <t>10,05; 15,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,59; 22,79</t>
+          <t>13,46; 22,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 14,19</t>
+          <t>5,71; 13,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,29</t>
+          <t>2,46; 8,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,15; 20,02</t>
+          <t>10,22; 20,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,92; 30,72</t>
+          <t>19,52; 30,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,2</t>
+          <t>1,86; 7,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 10,73</t>
+          <t>4,03; 11,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 13,73</t>
+          <t>5,33; 13,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,74; 20,87</t>
+          <t>8,95; 21,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,18</t>
+          <t>4,45; 9,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,67</t>
+          <t>3,96; 8,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 15,15</t>
+          <t>8,54; 14,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,24; 23,18</t>
+          <t>12,42; 22,91</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,49; 12,37</t>
+          <t>5,21; 11,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 11,23</t>
+          <t>4,89; 11,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,57</t>
+          <t>7,93; 16,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,4; 32,03</t>
+          <t>22,28; 31,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,93; 15,75</t>
+          <t>7,57; 15,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 17,78</t>
+          <t>9,36; 17,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,37; 17,92</t>
+          <t>9,35; 17,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,52; 24,49</t>
+          <t>17,25; 24,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,65</t>
+          <t>7,42; 12,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,93; 13,67</t>
+          <t>8,01; 13,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,64; 15,3</t>
+          <t>9,47; 15,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,11; 26,84</t>
+          <t>20,9; 27,01</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,93</t>
+          <t>5,1; 9,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,96</t>
+          <t>7,22; 11,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,56; 21,92</t>
+          <t>15,56; 22,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,56; 21,07</t>
+          <t>14,55; 20,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,61</t>
+          <t>6,35; 10,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,55; 13,99</t>
+          <t>8,98; 13,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,13; 23,8</t>
+          <t>17,04; 23,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 14,27</t>
+          <t>4,99; 14,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 9,42</t>
+          <t>6,34; 9,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,12</t>
+          <t>8,59; 12,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,0; 21,67</t>
+          <t>17,13; 21,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,31; 15,95</t>
+          <t>8,52; 16,32</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,0</t>
+          <t>4,5; 7,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,13</t>
+          <t>8,26; 13,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,05</t>
+          <t>10,17; 14,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 14,02</t>
+          <t>4,24; 14,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,42</t>
+          <t>5,6; 9,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,85; 12,25</t>
+          <t>7,79; 12,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,96; 14,83</t>
+          <t>9,9; 14,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,03; 20,95</t>
+          <t>16,11; 21,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,11</t>
+          <t>5,46; 8,27</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,55; 11,47</t>
+          <t>8,7; 11,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,79; 14,17</t>
+          <t>10,7; 14,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,56; 16,64</t>
+          <t>8,47; 16,58</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,17</t>
+          <t>6,35; 8,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,36; 9,4</t>
+          <t>7,37; 9,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,55; 13,76</t>
+          <t>11,37; 13,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,92; 18,61</t>
+          <t>13,45; 18,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,8; 9,81</t>
+          <t>7,82; 9,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,9; 10,99</t>
+          <t>8,98; 11,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,4</t>
+          <t>12,02; 14,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,16; 17,75</t>
+          <t>13,28; 17,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,68</t>
+          <t>7,42; 8,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,47; 9,87</t>
+          <t>8,48; 9,94</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,02; 13,74</t>
+          <t>12,02; 13,69</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,29; 17,84</t>
+          <t>14,35; 17,84</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20732; 43098</t>
+          <t>21674; 43909</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15105; 33068</t>
+          <t>15760; 34833</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24126; 46181</t>
+          <t>24099; 48080</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41050; 73724</t>
+          <t>41023; 73496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24266; 46717</t>
+          <t>23345; 45582</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17343; 38751</t>
+          <t>17485; 37678</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25123; 47941</t>
+          <t>25066; 49561</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36410; 53344</t>
+          <t>36199; 53529</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50567; 80204</t>
+          <t>49449; 81333</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35363; 63263</t>
+          <t>36928; 63998</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54462; 87714</t>
+          <t>54307; 89048</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83159; 123385</t>
+          <t>81649; 118150</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24674; 49416</t>
+          <t>25553; 51618</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16088; 41783</t>
+          <t>16949; 40874</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29703; 55508</t>
+          <t>29589; 53238</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61296; 101063</t>
+          <t>61682; 101745</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33942; 61418</t>
+          <t>34362; 60908</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27348; 50095</t>
+          <t>26534; 50222</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26998; 53456</t>
+          <t>28149; 55412</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73609; 102427</t>
+          <t>72913; 103255</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65111; 102814</t>
+          <t>66330; 102334</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49280; 83975</t>
+          <t>47348; 80440</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62574; 98718</t>
+          <t>63040; 99387</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>142813; 192039</t>
+          <t>143882; 193823</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14408; 33333</t>
+          <t>13791; 34647</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16146; 35469</t>
+          <t>16825; 36693</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21364; 41008</t>
+          <t>20198; 41110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47500; 74383</t>
+          <t>47955; 73736</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19626; 40808</t>
+          <t>20106; 42916</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35444; 61188</t>
+          <t>34755; 60691</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34092; 60724</t>
+          <t>35097; 61301</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63965; 88004</t>
+          <t>63134; 87360</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38916; 67674</t>
+          <t>37651; 66196</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55614; 89279</t>
+          <t>56712; 90240</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62022; 94920</t>
+          <t>60969; 93180</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>116154; 152551</t>
+          <t>117871; 153029</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13160; 31212</t>
+          <t>12089; 30327</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24934; 48223</t>
+          <t>25440; 49842</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31117; 56237</t>
+          <t>30824; 54063</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52259; 88222</t>
+          <t>52674; 86615</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25851; 48420</t>
+          <t>26162; 49002</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24598; 48393</t>
+          <t>24256; 46455</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38805; 68483</t>
+          <t>38002; 67199</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50402; 106176</t>
+          <t>47671; 105493</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43183; 71188</t>
+          <t>43662; 73017</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56206; 89002</t>
+          <t>55213; 88101</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75892; 113928</t>
+          <t>76077; 113907</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>107118; 179685</t>
+          <t>106087; 178899</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11996; 28850</t>
+          <t>11616; 27998</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5183; 17622</t>
+          <t>5235; 17950</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21445; 42283</t>
+          <t>21584; 42294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35611; 54912</t>
+          <t>34892; 54133</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3572; 14960</t>
+          <t>3861; 15342</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8478; 23557</t>
+          <t>8847; 24610</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11848; 30021</t>
+          <t>11659; 30246</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22626; 53998</t>
+          <t>23169; 55331</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18918; 37717</t>
+          <t>18287; 39607</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16769; 37464</t>
+          <t>17099; 37109</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37427; 65110</t>
+          <t>36714; 63157</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>57948; 101411</t>
+          <t>54335; 100247</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14869; 33507</t>
+          <t>14116; 31400</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13312; 30764</t>
+          <t>13411; 31458</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19867; 40972</t>
+          <t>20874; 42604</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60387; 86353</t>
+          <t>60067; 86218</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22067; 43808</t>
+          <t>21058; 43240</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26176; 49791</t>
+          <t>26218; 49327</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25600; 48936</t>
+          <t>25537; 48729</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>45035; 62964</t>
+          <t>44339; 63406</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41406; 69434</t>
+          <t>40714; 67201</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43922; 75725</t>
+          <t>44375; 73362</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51692; 82027</t>
+          <t>50756; 82148</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>111182; 141345</t>
+          <t>110087; 142269</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31838; 61090</t>
+          <t>31375; 58485</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48284; 79290</t>
+          <t>47860; 79143</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>102158; 143907</t>
+          <t>102164; 145156</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90892; 131548</t>
+          <t>90810; 129231</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>40898; 67713</t>
+          <t>40504; 68291</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59337; 97086</t>
+          <t>62283; 96687</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>118395; 164500</t>
+          <t>117806; 162285</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>45964; 121158</t>
+          <t>42336; 120909</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>78867; 117994</t>
+          <t>79416; 120207</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>117185; 164364</t>
+          <t>116600; 163689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>229071; 292078</t>
+          <t>230907; 292038</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>122515; 235075</t>
+          <t>125588; 240460</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33838; 59503</t>
+          <t>33441; 58920</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>66368; 102278</t>
+          <t>64376; 101878</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>79341; 117198</t>
+          <t>79176; 116413</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>36452; 130215</t>
+          <t>39422; 132333</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44863; 73802</t>
+          <t>43838; 72832</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64696; 100917</t>
+          <t>64214; 99057</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>82309; 122523</t>
+          <t>81820; 120704</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>115072; 150375</t>
+          <t>115610; 151426</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>84733; 123937</t>
+          <t>83349; 126284</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>136974; 183846</t>
+          <t>139431; 187365</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>173154; 227413</t>
+          <t>171705; 226398</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>140912; 274039</t>
+          <t>139440; 272983</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>209536; 267820</t>
+          <t>208080; 268121</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>252379; 322286</t>
+          <t>252517; 323157</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>391908; 467061</t>
+          <t>385915; 462648</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>446849; 643924</t>
+          <t>465285; 645945</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>263461; 331569</t>
+          <t>264324; 329422</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>316856; 391205</t>
+          <t>319615; 393320</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>422524; 510518</t>
+          <t>426087; 512579</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>488579; 659073</t>
+          <t>493102; 660438</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>489298; 577801</t>
+          <t>494099; 579992</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>591395; 689537</t>
+          <t>592116; 694341</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>834114; 953145</t>
+          <t>834380; 950192</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1025000; 1279680</t>
+          <t>1029354; 1279637</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 16,08</t>
+          <t>7,71; 15,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 11,82</t>
+          <t>5,55; 11,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,2; 16,37</t>
+          <t>8,09; 16,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,17; 23,6</t>
+          <t>14,2; 23,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 17,48</t>
+          <t>8,91; 17,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 13,12</t>
+          <t>5,78; 13,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 17,17</t>
+          <t>8,47; 17,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 18,48</t>
+          <t>12,18; 18,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 15,24</t>
+          <t>9,18; 14,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 11,0</t>
+          <t>6,24; 11,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,32; 15,29</t>
+          <t>9,43; 15,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,58; 19,66</t>
+          <t>14,01; 19,26</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 10,47</t>
+          <t>4,93; 10,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,09</t>
+          <t>3,31; 8,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,59</t>
+          <t>5,93; 10,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,9; 19,63</t>
+          <t>12,27; 19,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 12,09</t>
+          <t>7,01; 11,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,59</t>
+          <t>5,21; 9,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 10,59</t>
+          <t>5,41; 10,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,16; 20,05</t>
+          <t>13,75; 19,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,26</t>
+          <t>6,48; 10,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,82</t>
+          <t>4,75; 7,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,69</t>
+          <t>6,2; 9,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,92; 18,76</t>
+          <t>13,76; 18,39</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 10,87</t>
+          <t>4,21; 10,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 11,32</t>
+          <t>4,94; 11,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,9</t>
+          <t>6,69; 13,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,17; 23,33</t>
+          <t>15,5; 23,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,99; 12,79</t>
+          <t>5,98; 12,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 17,8</t>
+          <t>10,11; 17,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,44; 18,23</t>
+          <t>10,3; 17,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 25,02</t>
+          <t>18,31; 24,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 10,12</t>
+          <t>6,07; 10,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 13,57</t>
+          <t>8,56; 13,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 14,23</t>
+          <t>9,2; 14,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,72; 23,01</t>
+          <t>17,67; 22,89</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,46</t>
+          <t>3,51; 8,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,33</t>
+          <t>6,91; 13,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 14,61</t>
+          <t>8,23; 14,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,85; 27,71</t>
+          <t>17,52; 29,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 13,19</t>
+          <t>7,02; 13,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,24; 11,94</t>
+          <t>6,11; 11,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 17,35</t>
+          <t>9,95; 17,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 22,18</t>
+          <t>17,94; 24,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,98; 10,0</t>
+          <t>5,95; 9,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 11,55</t>
+          <t>7,23; 11,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 15,04</t>
+          <t>10,03; 15,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 22,69</t>
+          <t>18,92; 25,37</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 13,77</t>
+          <t>5,83; 14,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,44</t>
+          <t>2,45; 8,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 20,02</t>
+          <t>10,24; 19,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,52; 30,29</t>
+          <t>19,58; 30,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,39</t>
+          <t>1,87; 6,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 11,21</t>
+          <t>4,43; 11,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,84</t>
+          <t>5,51; 14,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 21,38</t>
+          <t>15,91; 23,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,64</t>
+          <t>4,65; 9,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,59</t>
+          <t>4,02; 8,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 14,69</t>
+          <t>8,82; 15,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,42; 22,91</t>
+          <t>18,91; 25,05</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 11,59</t>
+          <t>5,44; 11,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 11,48</t>
+          <t>4,91; 11,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,93; 16,19</t>
+          <t>7,55; 15,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,28; 31,98</t>
+          <t>22,74; 31,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,55</t>
+          <t>7,86; 15,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,36; 17,61</t>
+          <t>9,64; 17,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 17,84</t>
+          <t>9,6; 18,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,25; 24,67</t>
+          <t>17,88; 25,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,42; 12,24</t>
+          <t>7,29; 12,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,01; 13,24</t>
+          <t>7,75; 13,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,47; 15,32</t>
+          <t>9,62; 15,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,9; 27,01</t>
+          <t>21,47; 27,41</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,51</t>
+          <t>5,14; 9,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 11,94</t>
+          <t>7,02; 11,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,56; 22,11</t>
+          <t>15,43; 21,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,7</t>
+          <t>14,74; 21,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,7</t>
+          <t>6,28; 10,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,98; 13,93</t>
+          <t>8,79; 13,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,04; 23,48</t>
+          <t>17,1; 23,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 14,24</t>
+          <t>11,69; 15,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,34; 9,59</t>
+          <t>6,27; 9,43</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,59; 12,07</t>
+          <t>8,51; 12,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,13; 21,67</t>
+          <t>17,17; 21,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,52; 16,32</t>
+          <t>14,17; 17,61</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,92</t>
+          <t>4,45; 8,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,26; 13,08</t>
+          <t>8,27; 12,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,17; 14,95</t>
+          <t>10,23; 15,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,24; 14,25</t>
+          <t>11,2; 16,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,6; 9,3</t>
+          <t>5,85; 9,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,02</t>
+          <t>7,67; 11,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,9; 14,61</t>
+          <t>10,06; 14,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,11; 21,1</t>
+          <t>16,14; 20,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,27</t>
+          <t>5,52; 8,09</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,7; 11,69</t>
+          <t>8,7; 11,87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,7; 14,11</t>
+          <t>10,74; 14,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,47; 16,58</t>
+          <t>14,17; 17,78</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,18</t>
+          <t>6,39; 8,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,43</t>
+          <t>7,45; 9,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,37; 13,63</t>
+          <t>11,37; 13,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,45; 18,67</t>
+          <t>17,04; 19,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,82; 9,75</t>
+          <t>7,74; 9,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,98; 11,05</t>
+          <t>8,95; 11,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,02; 14,46</t>
+          <t>12,04; 14,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,28; 17,79</t>
+          <t>16,56; 18,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,71</t>
+          <t>7,36; 8,75</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,48; 9,94</t>
+          <t>8,53; 9,9</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,02; 13,69</t>
+          <t>12,0; 13,69</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,35; 17,84</t>
+          <t>17,19; 18,85</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54989</t>
+          <t>57835</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43903</t>
+          <t>46800</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98892</t>
+          <t>104635</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21674; 43909</t>
+          <t>21043; 43122</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15760; 34833</t>
+          <t>16356; 33524</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24099; 48080</t>
+          <t>23773; 47209</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41023; 73496</t>
+          <t>45272; 75117</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23345; 45582</t>
+          <t>23233; 45989</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17485; 37678</t>
+          <t>16613; 37642</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25066; 49561</t>
+          <t>24462; 49723</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36199; 53529</t>
+          <t>38502; 57669</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49449; 81333</t>
+          <t>48997; 79874</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36928; 63998</t>
+          <t>36335; 65054</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54307; 89048</t>
+          <t>54901; 87910</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81649; 118150</t>
+          <t>88967; 122299</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79646</t>
+          <t>83945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86845</t>
+          <t>88673</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>166492</t>
+          <t>172618</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25553; 51618</t>
+          <t>24303; 50254</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16949; 40874</t>
+          <t>16752; 41182</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29589; 53238</t>
+          <t>29818; 53911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61682; 101745</t>
+          <t>65109; 104906</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34362; 60908</t>
+          <t>35338; 60047</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26534; 50222</t>
+          <t>27302; 51438</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28149; 55412</t>
+          <t>28321; 53395</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72913; 103255</t>
+          <t>75158; 105965</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66330; 102334</t>
+          <t>64622; 100486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47348; 80440</t>
+          <t>48930; 81088</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63040; 99387</t>
+          <t>63563; 99375</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>143882; 193823</t>
+          <t>148240; 198060</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59697</t>
+          <t>60977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75065</t>
+          <t>75641</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>134763</t>
+          <t>136617</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13791; 34647</t>
+          <t>13424; 32772</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16825; 36693</t>
+          <t>16015; 36133</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20198; 41110</t>
+          <t>21317; 41517</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47955; 73736</t>
+          <t>48971; 73595</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20106; 42916</t>
+          <t>20064; 40501</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34755; 60691</t>
+          <t>34466; 60568</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35097; 61301</t>
+          <t>34648; 59914</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63134; 87360</t>
+          <t>65264; 87887</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37651; 66196</t>
+          <t>39686; 66922</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56712; 90240</t>
+          <t>56943; 90056</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60969; 93180</t>
+          <t>60266; 94179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>117871; 153029</t>
+          <t>118814; 153907</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67475</t>
+          <t>84307</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>81489</t>
+          <t>89145</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>148964</t>
+          <t>173452</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12089; 30327</t>
+          <t>12581; 31795</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25440; 49842</t>
+          <t>25840; 50088</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30824; 54063</t>
+          <t>30444; 54358</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52674; 86615</t>
+          <t>65378; 108356</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26162; 49002</t>
+          <t>26072; 49619</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24256; 46455</t>
+          <t>23747; 46359</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38002; 67199</t>
+          <t>38551; 67616</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47671; 105493</t>
+          <t>75682; 102708</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43662; 73017</t>
+          <t>43459; 72834</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55213; 88101</t>
+          <t>55144; 88526</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76077; 113907</t>
+          <t>75969; 114005</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>106087; 178899</t>
+          <t>150416; 201695</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44213</t>
+          <t>50987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41179</t>
+          <t>43880</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85392</t>
+          <t>94867</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11616; 27998</t>
+          <t>11862; 28945</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5235; 17950</t>
+          <t>5207; 17982</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21584; 42294</t>
+          <t>21628; 41797</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34892; 54133</t>
+          <t>40270; 62285</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3861; 15342</t>
+          <t>3889; 14294</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8847; 24610</t>
+          <t>9725; 25113</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11659; 30246</t>
+          <t>12044; 30997</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23169; 55331</t>
+          <t>36418; 52871</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18287; 39607</t>
+          <t>19116; 38958</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17099; 37109</t>
+          <t>17355; 37507</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36714; 63157</t>
+          <t>37919; 64810</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>54335; 100247</t>
+          <t>82177; 108872</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72481</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>53474</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>125955</t>
+          <t>129711</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14116; 31400</t>
+          <t>14724; 32470</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13411; 31458</t>
+          <t>13457; 32503</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20874; 42604</t>
+          <t>19854; 41731</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60067; 86218</t>
+          <t>61548; 86343</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21058; 43240</t>
+          <t>21872; 43172</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26218; 49327</t>
+          <t>27005; 49083</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25537; 48729</t>
+          <t>26218; 49343</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>44339; 63406</t>
+          <t>47159; 66051</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40714; 67201</t>
+          <t>40042; 68718</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44375; 73362</t>
+          <t>42910; 73290</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50756; 82148</t>
+          <t>51563; 81467</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>110087; 142269</t>
+          <t>114770; 146517</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109292</t>
+          <t>129645</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>87571</t>
+          <t>105248</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>196863</t>
+          <t>234893</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31375; 58485</t>
+          <t>31634; 58619</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47860; 79143</t>
+          <t>46522; 77621</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>102164; 145156</t>
+          <t>101336; 143505</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90810; 129231</t>
+          <t>106051; 152639</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>40504; 68291</t>
+          <t>40107; 68591</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62283; 96687</t>
+          <t>60969; 96904</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>117806; 162285</t>
+          <t>118177; 160912</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>42336; 120909</t>
+          <t>90285; 122016</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79416; 120207</t>
+          <t>78541; 118203</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>116600; 163689</t>
+          <t>115398; 163985</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>230907; 292038</t>
+          <t>231478; 290222</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>125588; 240460</t>
+          <t>211419; 262669</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91598</t>
+          <t>109570</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>132983</t>
+          <t>152147</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>224581</t>
+          <t>261717</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33441; 58920</t>
+          <t>33077; 59605</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>64376; 101878</t>
+          <t>64461; 100671</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>79176; 116413</t>
+          <t>79658; 117290</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>39422; 132333</t>
+          <t>89405; 128849</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>43838; 72832</t>
+          <t>45824; 76592</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64214; 99057</t>
+          <t>63199; 98058</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81820; 120704</t>
+          <t>83101; 122175</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>115610; 151426</t>
+          <t>134208; 174502</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>83349; 126284</t>
+          <t>84290; 123566</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>139431; 187365</t>
+          <t>139434; 190242</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>171705; 226398</t>
+          <t>172303; 226580</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>139440; 272983</t>
+          <t>230955; 289751</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>579391</t>
+          <t>650977</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>602510</t>
+          <t>657534</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1181902</t>
+          <t>1308510</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>208080; 268121</t>
+          <t>209412; 271884</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>252517; 323157</t>
+          <t>255201; 322954</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>385915; 462648</t>
+          <t>385870; 468053</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>465285; 645945</t>
+          <t>601919; 699677</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>264324; 329422</t>
+          <t>261588; 329584</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>319615; 393320</t>
+          <t>318571; 393250</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>426087; 512579</t>
+          <t>426715; 512088</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>493102; 660438</t>
+          <t>618777; 694281</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>494099; 579992</t>
+          <t>489979; 582606</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>592116; 694341</t>
+          <t>595702; 691765</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>834380; 950192</t>
+          <t>832352; 950207</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1029354; 1279637</t>
+          <t>1249391; 1369989</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
+          <t>Población que conforma un hogar unipersonal (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
+          <t>Población que conforma un hogar unipersonal (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
